--- a/hira_material_automation/raw/202601_202605__arthroscopy_cannula__041001.xlsx
+++ b/hira_material_automation/raw/202601_202605__arthroscopy_cannula__041001.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>청구현황(단위_개, 원)_202601_202605</t>
   </si>
@@ -48,6 +48,9 @@
   </si>
   <si>
     <t>041001</t>
+  </si>
+  <si>
+    <t>관절경 CANNULA</t>
   </si>
   <si>
     <t>2026년 02월</t>
@@ -192,7 +195,9 @@
       <c r="B5" t="s" s="3">
         <v>11</v>
       </c>
-      <c r="C5"/>
+      <c r="C5" t="s" s="3">
+        <v>12</v>
+      </c>
       <c r="D5" t="n" s="5">
         <v>23752.0</v>
       </c>
@@ -208,12 +213,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s" s="3">
         <v>11</v>
       </c>
-      <c r="C6"/>
+      <c r="C6" t="s" s="3">
+        <v>12</v>
+      </c>
       <c r="D6" t="n" s="5">
         <v>22600.0</v>
       </c>
@@ -229,12 +236,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s" s="3">
         <v>11</v>
       </c>
-      <c r="C7"/>
+      <c r="C7" t="s" s="3">
+        <v>12</v>
+      </c>
       <c r="D7" t="n" s="5">
         <v>22435.0</v>
       </c>
